--- a/data/data_dictionary.xlsx
+++ b/data/data_dictionary.xlsx
@@ -38,7 +38,7 @@
     <t>범위: 수강생에게 배포하는 Day1~3 파일(d1_buyers_raw · d1_invoices · d2_start · fx_krw_daily · d2_news · d3_start_features · d3_start_scoring · d3_features_panel · labs/day3/fx_forecast_inputs)의 컬럼 뜻·단위·출처</t>
   </si>
   <si>
-    <t>시트: columns(컬럼 사전) · codes(코드표) · payment_terms_map(결제조건 표기 → 정본 코드) · files(파일 목록) · changelog</t>
+    <t>시트: columns(컬럼 사전) · codes(코드표) · payment_terms_map(결제조건 표기 → 표준 코드) · files(파일 목록) · changelog</t>
   </si>
   <si>
     <t>dtype 열: 그 컬럼이 담는 값의 정의상 형식(text · number · integer · date · number/text)</t>
@@ -905,7 +905,7 @@
     <t>PRIVATE / UN(UN 계열 기구) / MDB(다자개발은행 재원 사업) / EM_GOV(신흥국 정부) / DM_GOV(선진국 정부)</t>
   </si>
   <si>
-    <t>담당자가 입력한 결제조건 그대로. 정본 코드 7종(codes 시트 payment_method)으로 바꿔 쓴다 — 표기별 코드는 payment_terms_map 시트</t>
+    <t>담당자가 입력한 결제조건 그대로. 표준 코드 7종(codes 시트 payment_method)으로 바꿔 쓴다 — 표기별 코드는 payment_terms_map 시트</t>
   </si>
   <si>
     <t>기준일(2026-09-30) 미결제 잔액(청구 통화 기준)</t>
@@ -956,7 +956,7 @@
     <t>선적일 = B/L일로 가정</t>
   </si>
   <si>
-    <t>정본 코드 7종 TT_ADV / TT_SPLIT_30_70 / OA / DA / DP / LC_SIGHT / LC_USANCE(codes 시트 payment_method)</t>
+    <t>표준 코드 7종 TT_ADV / TT_SPLIT_30_70 / OA / DA / DP / LC_SIGHT / LC_USANCE(codes 시트 payment_method)</t>
   </si>
   <si>
     <t>선적(B/L) 후 결제기일까지 일수. 선수금·D/P·L/C 일람불 = 0</t>
@@ -1325,19 +1325,19 @@
     <t>1</t>
   </si>
   <si>
-    <t>1 🟣</t>
+    <t>1</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>2 🟣</t>
+    <t>2</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>3 🔵🟣</t>
+    <t>3</t>
   </si>
   <si>
     <t>code_group</t>
@@ -1835,10 +1835,10 @@
     <t>USANCE L/C 90 DAYS</t>
   </si>
   <si>
-    <t>실습 기본 코드표(= 템플릿 00_코드표). 일부 표기는 일부러 빠져 있음 — 실습에서 '미분류'로 나오는 표기를 찾아 한 줄씩 추가</t>
-  </si>
-  <si>
-    <t>raw_upper = Excel UPPER(TRIM(원천)) 결과 — XLOOKUP 키</t>
+    <t>실습 기본 코드표(결제조건 표기 → 표준 코드). 내 코드표와 맞춰 볼 때 쓴다</t>
+  </si>
+  <si>
+    <t>raw_upper = 원천 표기를 TRIM · UPPER한 값 — 찾기(조회) 키</t>
   </si>
   <si>
     <t>path</t>
@@ -1904,13 +1904,13 @@
     <t>준비</t>
   </si>
   <si>
-    <t>바이어 스냅샷(기준일 2026-09-30). 원천 입력 오류 포함 — 무엇인지는 Lab2에서 찾는다. 시트 buyers(안내: readme)</t>
+    <t>바이어 스냅샷(기준일 2026-09-30). 원천 입력 오류 포함 — 1일차 실습 B에서 진단한다. 시트 buyers(안내: readme)</t>
   </si>
   <si>
     <t>인보이스 원장 36개월(2023-10~2026-09). 시트 invoices(안내: readme)</t>
   </si>
   <si>
-    <t>Day2 시작 파일(Day2 아침 공개). 시트 buyers(기준일 2026-08-31) · buyer_features_raw · fx_at_ref · invoices_raw(🟣) · dirty_list · map_ccy · map_country · dictionary</t>
+    <t>Day2 시작 파일(Day2 아침 공개). 시트 buyers(기준일 2026-08-31) · buyer_features_raw · fx_at_ref · invoices_raw · dirty_list · map_ccy · map_country · dictionary</t>
   </si>
   <si>
     <t>최근 300 관측일 원화 환율(FRED H.10 교차환율)</t>
@@ -1925,7 +1925,7 @@
     <t>Day3 학습 파일: 150개사 × 기준일 2개(2026-02-28·08-31)의 특성 + late_30d. split_suggested = 바이어 단위 70/30. Day3 아침 공개</t>
   </si>
   <si>
-    <t>Day3 점수화 파일: 기준일 2026-09-30, 같은 특성, 라벨 없음(Orange Predictions 입력)</t>
+    <t>Day3 점수화 파일: 기준일 2026-09-30, 같은 특성, 라벨 없음(모델 점수화 입력)</t>
   </si>
   <si>
     <t>바이어×월 패널(월말 2024-01~2026-08, 거래 중 바이어) + late_30d. split_suggested = 시간 분할(burn_in·train·test)</t>
@@ -1973,13 +1973,13 @@
     <t>Day2·3 파일 추가(d2_news · d3_start_features · d3_start_scoring · d3_features_panel · fx_forecast_inputs)</t>
   </si>
   <si>
-    <t>03 Part1 §4 사양 구현. 환율은 ECOS 키 확보 전이라 FRED H.10 교차환율 사용</t>
+    <t>데이터 사양 구현. 환율은 ECOS 키 확보 전이라 FRED H.10 교차환율 사용</t>
   </si>
   <si>
     <t>실존 기업명과 비슷한 가상 상호를 바꿈 · 사전에는 수강생 파일의 컬럼 뜻·단위·출처만 적음</t>
   </si>
   <si>
-    <t>03 Part1 §4.9·03 Part2 §2·§3 — Day2 특성의 정본 이름·정의와 Day3 입력</t>
+    <t>Day2 특성의 이름·정의와 Day3 입력</t>
   </si>
 </sst>
 </file>
